--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_65307_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_65307_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3dcb9b1ddcb44380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R860d0af677ab4249"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Lima / Prov: Huarochiri / Dist.: San Antonio</x:t>
+          <x:t>Dpto: Lima / Prov: Huarochirí / Dist.: San Antonio</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2504</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2463</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2492</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2433</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_65307_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_65307_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R860d0af677ab4249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcbda9f2bd3374b9e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,261 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2504</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2592</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2688</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
